--- a/Document/CycloInverter/Cycloinverter.xlsx
+++ b/Document/CycloInverter/Cycloinverter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\PowerrToplogyStudy\PowerToplogyStudy\Document\CycloInverter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2DCA92-3943-4E5B-9F34-79933DCB9B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB31576-58A3-445D-8869-C404918D3517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,13 +90,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -111,12 +124,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -536,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:X54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="29.28515625" customWidth="1"/>
@@ -558,7 +572,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:19" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>11</v>
       </c>
@@ -580,15 +594,36 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R24" t="s">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="R24" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R25" s="2" t="s">
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+    </row>
+    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="R25" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+    </row>
+    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
     </row>
     <row r="54" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
